--- a/模型訓練過程/discard模型訓練過程.xlsx
+++ b/模型訓練過程/discard模型訓練過程.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\專題\模型訓練過程\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A573EAA-BF61-4EC8-9F59-A97007396524}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46736B1E-3815-4B93-8579-C477514749BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="20">
   <si>
     <t>層數</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -89,35 +89,23 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>驗證準確率</t>
+    <t>45小時</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>模型名稱</t>
+    <t>42小時</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>CNN_300</t>
+    <t>39小時</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>CNN_400</t>
+    <t>36小時</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>CNN_400_Bat_Res</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CNN_512</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CNN_512_Bat</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CNN_512_Bat_Res</t>
+    <t>33小時</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -191,6 +179,4516 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-TW"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" altLang="zh-TW"/>
+              <a:t>10_256</a:t>
+            </a:r>
+            <a:endParaRPr lang="zh-TW" altLang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-TW"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>工作表1!$A$45:$A$49</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>33小時</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>36小時</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>39小時</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>42小時</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>45小時</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>工作表1!$B$45:$B$49</c:f>
+              <c:numCache>
+                <c:formatCode>0.00%</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0.26419999999999999</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.27839999999999998</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.28410000000000002</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.32950000000000002</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.3125</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-77B4-42A7-AECF-AEF546EF1507}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="1156829743"/>
+        <c:axId val="1156830575"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1156829743"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-TW"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1156830575"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1156830575"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.00%" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-TW"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1156829743"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="zh-TW"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-TW"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" altLang="zh-TW"/>
+              <a:t>15_256</a:t>
+            </a:r>
+            <a:endParaRPr lang="zh-TW" altLang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-TW"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>工作表1!$A$56:$A$60</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>33小時</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>36小時</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>39小時</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>42小時</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>45小時</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>工作表1!$B$56:$B$60</c:f>
+              <c:numCache>
+                <c:formatCode>0.00%</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0.2641</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.28889999999999999</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.30109999999999998</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.31819999999999998</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.28410000000000002</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-5C17-44A5-9A3C-D85FFD394960}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="1592369759"/>
+        <c:axId val="1592371423"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1592369759"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-TW"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1592371423"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1592371423"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.00%" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-TW"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1592369759"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="zh-TW"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-TW"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" altLang="zh-TW"/>
+              <a:t>15_512</a:t>
+            </a:r>
+            <a:endParaRPr lang="zh-TW" altLang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-TW"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>工作表1!$A$67:$A$71</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>33小時</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>36小時</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>39小時</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>42小時</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>45小時</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>工作表1!$B$67:$B$71</c:f>
+              <c:numCache>
+                <c:formatCode>0.00%</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0.2727</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.32390000000000002</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.30109999999999998</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.34089999999999998</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.34660000000000002</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-B820-47D3-9C2A-BE0686127F7E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="1591940287"/>
+        <c:axId val="1591941951"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1591940287"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-TW"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1591941951"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1591941951"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.00%" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-TW"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1591940287"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="zh-TW"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-TW"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" altLang="zh-TW"/>
+              <a:t>20_256</a:t>
+            </a:r>
+            <a:endParaRPr lang="zh-TW" altLang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-TW"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>工作表1!$A$78:$A$82</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>33小時</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>36小時</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>39小時</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>42小時</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>45小時</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>工作表1!$B$78:$B$82</c:f>
+              <c:numCache>
+                <c:formatCode>0.00%</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0.25779999999999997</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.27079999999999999</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.29430000000000001</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.28910000000000002</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.27339999999999998</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-D4AD-4A6F-BA75-0DDCA042D5E4}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="1595811551"/>
+        <c:axId val="1595808639"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1595811551"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-TW"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1595808639"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1595808639"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.00%" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-TW"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1595811551"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="zh-TW"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-TW"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" altLang="zh-TW"/>
+              <a:t>20_512</a:t>
+            </a:r>
+            <a:endParaRPr lang="zh-TW" altLang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-TW"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>工作表1!$A$89:$A$93</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>33小時</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>36小時</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>39小時</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>42小時</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>45小時</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>工作表1!$B$89:$B$93</c:f>
+              <c:numCache>
+                <c:formatCode>0.00%</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0.27079999999999999</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.29170000000000001</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.33069999999999999</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.29430000000000001</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.35680000000000001</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-54ED-4A92-BD76-E6EF22943F7C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="1543554335"/>
+        <c:axId val="1543555167"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1543554335"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-TW"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1543555167"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1543555167"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.00%" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-TW"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1543554335"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="zh-TW"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>342900</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>80962</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>23812</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="圖表 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{50300F8A-4F8C-43FB-9F0B-D2A2CB41553C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>309562</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>23812</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>4762</xdr:colOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>166687</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="6" name="圖表 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7F92CDE9-166D-441D-9DC8-67658DD2B376}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>223837</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>4762</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>528637</xdr:colOff>
+      <xdr:row>77</xdr:row>
+      <xdr:rowOff>147637</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="7" name="圖表 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8222B900-8740-4AA2-B2A9-9792FF4CCA79}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>109537</xdr:colOff>
+      <xdr:row>78</xdr:row>
+      <xdr:rowOff>90487</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>414337</xdr:colOff>
+      <xdr:row>92</xdr:row>
+      <xdr:rowOff>33337</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="9" name="圖表 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CF1068A8-66CD-44D0-A1A4-4747BFA09D2C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>433387</xdr:colOff>
+      <xdr:row>90</xdr:row>
+      <xdr:rowOff>147637</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>366712</xdr:colOff>
+      <xdr:row>104</xdr:row>
+      <xdr:rowOff>90487</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="10" name="圖表 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{621126E9-E618-49A9-9AD4-531F8CC77F77}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -456,7 +4954,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H129"/>
+  <dimension ref="A1:H94"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.7109375" customWidth="1"/>
@@ -848,7 +5346,7 @@
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="B41" t="s">
         <v>0</v>
@@ -874,629 +5372,515 @@
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="B42">
         <v>10</v>
       </c>
       <c r="C42">
-        <v>300</v>
+        <v>256</v>
       </c>
       <c r="D42">
         <v>32</v>
       </c>
       <c r="E42">
-        <v>1E-4</v>
+        <v>1E-3</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G42" s="3">
-        <v>45926.586111111108</v>
-      </c>
+      <c r="G42" s="3"/>
       <c r="H42" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="B44" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B45" s="4">
+        <v>0.26419999999999999</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B46" s="4">
+        <v>0.27839999999999998</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B47" s="4">
+        <v>0.28410000000000002</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B48" s="4">
+        <v>0.32950000000000002</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" s="2" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A45" s="4">
+      <c r="B49" s="4">
         <v>0.3125</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>6</v>
-      </c>
-      <c r="B47" t="s">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>59.375</v>
+      </c>
+      <c r="B50" s="4">
+        <v>0.3216</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B51" s="4"/>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>10</v>
+      </c>
+      <c r="B52" t="s">
+        <v>0</v>
+      </c>
+      <c r="C52" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>4</v>
+      </c>
+      <c r="B53">
         <v>15</v>
       </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A48" s="2">
-        <v>0.875</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A49" s="2">
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A50" s="2">
-        <v>0.625</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A51" s="2">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A52" s="2">
-        <v>0.375</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A53" s="2">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A54" s="2">
-        <v>0.125</v>
+      <c r="C53">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>13</v>
+      </c>
+      <c r="B55" t="s">
+        <v>9</v>
+      </c>
+      <c r="D55" t="s">
+        <v>1</v>
+      </c>
+      <c r="E55" t="s">
+        <v>2</v>
+      </c>
+      <c r="F55" t="s">
+        <v>3</v>
+      </c>
+      <c r="G55" t="s">
+        <v>7</v>
+      </c>
+      <c r="H55" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
+      <c r="A56" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B56" s="4">
+        <v>0.2641</v>
+      </c>
+      <c r="D56">
+        <v>32</v>
+      </c>
+      <c r="E56">
+        <v>1E-3</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G56" s="3"/>
+      <c r="H56" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B57" s="4">
+        <v>0.28889999999999999</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B58" s="4">
+        <v>0.30109999999999998</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B59" s="4">
+        <v>0.31819999999999998</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B60" s="4">
+        <v>0.28410000000000002</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61">
+        <v>62.5</v>
+      </c>
+      <c r="B61" s="4">
+        <v>0.26989999999999997</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
         <v>10</v>
       </c>
-      <c r="B56" t="s">
+      <c r="B63" t="s">
         <v>0</v>
       </c>
-      <c r="C56" t="s">
+      <c r="C63" t="s">
         <v>14</v>
       </c>
-      <c r="D56" t="s">
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>4</v>
+      </c>
+      <c r="B64">
+        <v>15</v>
+      </c>
+      <c r="C64">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>13</v>
+      </c>
+      <c r="B66" t="s">
+        <v>9</v>
+      </c>
+      <c r="D66" t="s">
         <v>1</v>
       </c>
-      <c r="E56" t="s">
+      <c r="E66" t="s">
         <v>2</v>
       </c>
-      <c r="F56" t="s">
+      <c r="F66" t="s">
         <v>3</v>
       </c>
-      <c r="G56" t="s">
+      <c r="G66" t="s">
         <v>7</v>
       </c>
-      <c r="H56" t="s">
+      <c r="H66" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B67" s="4">
+        <v>0.2727</v>
+      </c>
+      <c r="D67">
+        <v>32</v>
+      </c>
+      <c r="E67">
+        <v>1E-3</v>
+      </c>
+      <c r="F67" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G67" s="3"/>
+      <c r="H67" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A68" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B57">
-        <v>10</v>
-      </c>
-      <c r="C57">
-        <v>400</v>
-      </c>
-      <c r="D57">
-        <v>32</v>
-      </c>
-      <c r="E57">
-        <v>1E-4</v>
-      </c>
-      <c r="F57" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G57" s="3">
-        <v>45926.585416666669</v>
-      </c>
-      <c r="H57" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
-        <v>8</v>
-      </c>
-      <c r="B59" t="s">
+      <c r="B68" s="4">
+        <v>0.32390000000000002</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A69" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B69" s="4">
+        <v>0.30109999999999998</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B70" s="4">
+        <v>0.34089999999999998</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A71" s="2" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A60" s="4">
-        <v>0.3125</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
-        <v>6</v>
-      </c>
-      <c r="B62" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A63" s="2">
-        <v>0.875</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A64" s="2">
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A65" s="2">
-        <v>0.625</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A66" s="2">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A67" s="2">
-        <v>0.375</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A68" s="2">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A69" s="2">
-        <v>0.125</v>
-      </c>
-    </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
-        <v>10</v>
-      </c>
-      <c r="B71" t="s">
-        <v>0</v>
-      </c>
-      <c r="C71" t="s">
-        <v>14</v>
-      </c>
-      <c r="D71" t="s">
-        <v>1</v>
-      </c>
-      <c r="E71" t="s">
-        <v>2</v>
-      </c>
-      <c r="F71" t="s">
-        <v>3</v>
-      </c>
-      <c r="G71" t="s">
-        <v>7</v>
-      </c>
-      <c r="H71" t="s">
-        <v>11</v>
+      <c r="B71" s="4">
+        <v>0.34660000000000002</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A72" t="s">
-        <v>19</v>
-      </c>
-      <c r="B72">
-        <v>10</v>
-      </c>
-      <c r="C72">
-        <v>400</v>
-      </c>
-      <c r="D72">
-        <v>32</v>
-      </c>
-      <c r="E72">
-        <v>1E-4</v>
-      </c>
-      <c r="F72" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G72" s="3">
-        <v>45926.585416666669</v>
-      </c>
-      <c r="H72" t="s">
-        <v>12</v>
+      <c r="A72">
+        <v>59.375</v>
+      </c>
+      <c r="B72" s="4">
+        <v>0.35799999999999998</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B74" t="s">
-        <v>15</v>
+        <v>0</v>
+      </c>
+      <c r="C74" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A75" s="4">
-        <v>0.4375</v>
+      <c r="A75" t="s">
+        <v>4</v>
+      </c>
+      <c r="B75">
+        <v>20</v>
+      </c>
+      <c r="C75">
+        <v>256</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="B77" t="s">
+        <v>9</v>
+      </c>
+      <c r="D77" t="s">
+        <v>1</v>
+      </c>
+      <c r="E77" t="s">
+        <v>2</v>
+      </c>
+      <c r="F77" t="s">
+        <v>3</v>
+      </c>
+      <c r="G77" t="s">
+        <v>7</v>
+      </c>
+      <c r="H77" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A78" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B78" s="4">
+        <v>0.25779999999999997</v>
+      </c>
+      <c r="D78">
+        <v>32</v>
+      </c>
+      <c r="E78">
+        <v>1E-3</v>
+      </c>
+      <c r="F78" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G78" s="3"/>
+      <c r="H78" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A79" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B79" s="4">
+        <v>0.27079999999999999</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A80" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B80" s="4">
+        <v>0.29430000000000001</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A81" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B81" s="4">
+        <v>0.28910000000000002</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A82" s="2" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A78" s="2">
-        <v>0.875</v>
-      </c>
-    </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A79" s="2">
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A80" s="2">
-        <v>0.625</v>
-      </c>
-    </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A81" s="2">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A82" s="2">
-        <v>0.375</v>
+      <c r="B82" s="4">
+        <v>0.27339999999999998</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A83" s="2">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A84" s="2">
-        <v>0.125</v>
+      <c r="A83">
+        <v>56.25</v>
+      </c>
+      <c r="B83" s="4">
+        <v>0.26819999999999999</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>10</v>
+      </c>
+      <c r="B85" t="s">
+        <v>0</v>
+      </c>
+      <c r="C85" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>10</v>
-      </c>
-      <c r="B86" t="s">
-        <v>0</v>
-      </c>
-      <c r="C86" t="s">
-        <v>14</v>
-      </c>
-      <c r="D86" t="s">
+        <v>4</v>
+      </c>
+      <c r="B86">
+        <v>20</v>
+      </c>
+      <c r="C86">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>13</v>
+      </c>
+      <c r="B88" t="s">
+        <v>9</v>
+      </c>
+      <c r="D88" t="s">
         <v>1</v>
       </c>
-      <c r="E86" t="s">
+      <c r="E88" t="s">
         <v>2</v>
       </c>
-      <c r="F86" t="s">
+      <c r="F88" t="s">
         <v>3</v>
       </c>
-      <c r="G86" t="s">
+      <c r="G88" t="s">
         <v>7</v>
       </c>
-      <c r="H86" t="s">
+      <c r="H88" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A87" t="s">
-        <v>20</v>
-      </c>
-      <c r="B87">
-        <v>10</v>
-      </c>
-      <c r="C87">
-        <v>512</v>
-      </c>
-      <c r="D87">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A89" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B89" s="4">
+        <v>0.27079999999999999</v>
+      </c>
+      <c r="D89">
         <v>32</v>
       </c>
-      <c r="E87">
-        <v>1E-4</v>
-      </c>
-      <c r="F87" s="1" t="s">
+      <c r="E89">
+        <v>1E-3</v>
+      </c>
+      <c r="F89" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G87" s="3">
-        <v>45926.585416666669</v>
-      </c>
-      <c r="H87" t="s">
+      <c r="G89" s="3"/>
+      <c r="H89" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A89" t="s">
-        <v>8</v>
-      </c>
-      <c r="B89" t="s">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A90" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B90" s="4">
+        <v>0.29170000000000001</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A91" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B91" s="4">
+        <v>0.33069999999999999</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A92" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B92" s="4">
+        <v>0.29430000000000001</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A93" s="2" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A90" s="4">
-        <v>0.34375</v>
-      </c>
-    </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A92" t="s">
-        <v>6</v>
-      </c>
-      <c r="B92" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A93" s="2">
-        <v>0.875</v>
+      <c r="B93" s="4">
+        <v>0.35680000000000001</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A94" s="2">
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A95" s="2">
-        <v>0.625</v>
-      </c>
-    </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A96" s="2">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A97" s="2">
-        <v>0.375</v>
-      </c>
-    </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A98" s="2">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A99" s="2">
-        <v>0.125</v>
-      </c>
-    </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A101" t="s">
-        <v>10</v>
-      </c>
-      <c r="B101" t="s">
-        <v>0</v>
-      </c>
-      <c r="C101" t="s">
-        <v>14</v>
-      </c>
-      <c r="D101" t="s">
-        <v>1</v>
-      </c>
-      <c r="E101" t="s">
-        <v>2</v>
-      </c>
-      <c r="F101" t="s">
-        <v>3</v>
-      </c>
-      <c r="G101" t="s">
-        <v>7</v>
-      </c>
-      <c r="H101" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A102" t="s">
-        <v>21</v>
-      </c>
-      <c r="B102">
-        <v>10</v>
-      </c>
-      <c r="C102">
-        <v>512</v>
-      </c>
-      <c r="D102">
-        <v>32</v>
-      </c>
-      <c r="E102">
-        <v>1E-4</v>
-      </c>
-      <c r="F102" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G102" s="3">
-        <v>45926.585416666669</v>
-      </c>
-      <c r="H102" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A104" t="s">
-        <v>8</v>
-      </c>
-      <c r="B104" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A105" s="4">
-        <v>0.46875</v>
-      </c>
-    </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A107" t="s">
-        <v>6</v>
-      </c>
-      <c r="B107" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A108" s="2">
-        <v>0.875</v>
-      </c>
-    </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A109" s="2">
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A110" s="2">
-        <v>0.625</v>
-      </c>
-    </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A111" s="2">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A112" s="2">
-        <v>0.375</v>
-      </c>
-    </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A113" s="2">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A114" s="2">
-        <v>0.125</v>
-      </c>
-    </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A116" t="s">
-        <v>10</v>
-      </c>
-      <c r="B116" t="s">
-        <v>0</v>
-      </c>
-      <c r="C116" t="s">
-        <v>14</v>
-      </c>
-      <c r="D116" t="s">
-        <v>1</v>
-      </c>
-      <c r="E116" t="s">
-        <v>2</v>
-      </c>
-      <c r="F116" t="s">
-        <v>3</v>
-      </c>
-      <c r="G116" t="s">
-        <v>7</v>
-      </c>
-      <c r="H116" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A117" t="s">
-        <v>22</v>
-      </c>
-      <c r="B117">
-        <v>10</v>
-      </c>
-      <c r="C117">
-        <v>512</v>
-      </c>
-      <c r="D117">
-        <v>32</v>
-      </c>
-      <c r="E117">
-        <v>1E-4</v>
-      </c>
-      <c r="F117" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G117" s="3">
-        <v>45926.585416666669</v>
-      </c>
-      <c r="H117" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A119" t="s">
-        <v>8</v>
-      </c>
-      <c r="B119" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A120" s="4">
-        <v>0.375</v>
-      </c>
-    </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A122" t="s">
-        <v>6</v>
-      </c>
-      <c r="B122" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A123" s="2">
-        <v>0.875</v>
-      </c>
-    </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A124" s="2">
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A125" s="2">
-        <v>0.625</v>
-      </c>
-    </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A126" s="2">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A127" s="2">
-        <v>0.375</v>
-      </c>
-    </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A128" s="2">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="129" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A129" s="2">
-        <v>0.125</v>
+      <c r="A94">
+        <v>59.375</v>
+      </c>
+      <c r="B94" s="4">
+        <v>0.33069999999999999</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>